--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-19).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-19).xlsx
@@ -938,19 +938,19 @@
     <t>215</t>
   </si>
   <si>
-    <t>32</t>
+    <t>23</t>
   </si>
   <si>
-    <t>R$ 3.619,68</t>
+    <t>R$ 3.598,16</t>
   </si>
   <si>
-    <t>41.8</t>
+    <t>41.3</t>
   </si>
   <si>
-    <t>25.9</t>
+    <t>25.7</t>
   </si>
   <si>
-    <t>4.54</t>
+    <t>4.60</t>
   </si>
   <si>
     <t>18.2</t>
@@ -959,22 +959,22 @@
     <t>7.2</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>45.6%</t>
+    <t>45.9%</t>
   </si>
   <si>
-    <t>19.3%</t>
+    <t>19.0%</t>
   </si>
   <si>
-    <t>1.5%</t>
+    <t>1.4%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>4.4%</t>
+    <t>4.3%</t>
   </si>
   <si>
     <t>1.0%</t>
@@ -983,43 +983,37 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>8.0%</t>
+    <t>7.9%</t>
   </si>
   <si>
     <t>3.2%</t>
   </si>
   <si>
-    <t>4.5%</t>
+    <t>1119.0</t>
   </si>
   <si>
-    <t>1088.0</t>
+    <t>936.0</t>
   </si>
   <si>
-    <t>910.0</t>
+    <t>70.0</t>
   </si>
   <si>
-    <t>69.0</t>
+    <t>13.0</t>
   </si>
   <si>
-    <t>12.0</t>
+    <t>214.0</t>
   </si>
   <si>
-    <t>209.0</t>
+    <t>48.0</t>
   </si>
   <si>
-    <t>46.0</t>
+    <t>5.0</t>
   </si>
   <si>
-    <t>4.0</t>
+    <t>387.0</t>
   </si>
   <si>
-    <t>375.0</t>
-  </si>
-  <si>
-    <t>152.0</t>
-  </si>
-  <si>
-    <t>210.0</t>
+    <t>158.0</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -2212,7 +2206,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2242,35 +2236,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>7634.3199999999997</v>
+      </c>
+      <c r="N6" s="6">
+        <v>79</v>
+      </c>
+      <c r="O6" s="6">
+        <v>62</v>
+      </c>
+      <c r="P6" s="7">
+        <v>3.9565405063291141</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>12.611020967741934</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.6486564516129032</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.080645161290322578</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.048387096774193547</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9135,7 +9187,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9165,8 +9217,12 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>0</v>
+      </c>
+      <c r="N51" s="6">
+        <v>0</v>
+      </c>
       <c r="O51" s="6"/>
       <c r="P51" s="7"/>
       <c r="Q51" s="8"/>
@@ -10204,33 +10260,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>34</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -11052,7 +11154,7 @@
         <v>19633</v>
       </c>
       <c r="B64" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C64" s="4">
         <v>51</v>
@@ -11080,35 +11182,93 @@
         <v>58</v>
       </c>
       <c r="L64" s="4"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="8"/>
-      <c r="R64" s="8"/>
-      <c r="S64" s="8"/>
-      <c r="T64" s="9"/>
-      <c r="U64" s="9"/>
-      <c r="V64" s="9"/>
-      <c r="W64" s="9"/>
-      <c r="X64" s="9"/>
-      <c r="Y64" s="9"/>
-      <c r="Z64" s="9"/>
-      <c r="AA64" s="9"/>
-      <c r="AB64" s="9"/>
-      <c r="AC64" s="9"/>
-      <c r="AD64" s="6"/>
-      <c r="AE64" s="6"/>
-      <c r="AF64" s="6"/>
-      <c r="AG64" s="6"/>
-      <c r="AH64" s="6"/>
-      <c r="AI64" s="6"/>
-      <c r="AJ64" s="6"/>
-      <c r="AK64" s="6"/>
-      <c r="AL64" s="6"/>
-      <c r="AM64" s="6"/>
-      <c r="AN64" s="9"/>
-      <c r="AO64" s="6"/>
+      <c r="M64" s="5">
+        <v>3458.3000000000002</v>
+      </c>
+      <c r="N64" s="6">
+        <v>35</v>
+      </c>
+      <c r="O64" s="6">
+        <v>16</v>
+      </c>
+      <c r="P64" s="7">
+        <v>6.6873727272727272</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>18.11145625</v>
+      </c>
+      <c r="R64" s="8">
+        <v>9.5320538461538469</v>
+      </c>
+      <c r="S64" s="8">
+        <v>7</v>
+      </c>
+      <c r="T64" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="U64" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="V64" s="9">
+        <v>0</v>
+      </c>
+      <c r="W64" s="9">
+        <v>0</v>
+      </c>
+      <c r="X64" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="Y64" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Z64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="AB64" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AC64" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AD64" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE64" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF64" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI64" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ64" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL64" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM64" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP64" s="4">
         <v>58</v>
       </c>
@@ -13938,7 +14098,7 @@
         <v>19685</v>
       </c>
       <c r="B84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C84" s="4">
         <v>51</v>
@@ -13968,35 +14128,93 @@
         <v>58</v>
       </c>
       <c r="L84" s="4"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="6"/>
-      <c r="O84" s="6"/>
-      <c r="P84" s="7"/>
-      <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
-      <c r="S84" s="8"/>
-      <c r="T84" s="9"/>
-      <c r="U84" s="9"/>
-      <c r="V84" s="9"/>
-      <c r="W84" s="9"/>
-      <c r="X84" s="9"/>
-      <c r="Y84" s="9"/>
-      <c r="Z84" s="9"/>
-      <c r="AA84" s="9"/>
-      <c r="AB84" s="9"/>
-      <c r="AC84" s="9"/>
-      <c r="AD84" s="6"/>
-      <c r="AE84" s="6"/>
-      <c r="AF84" s="6"/>
-      <c r="AG84" s="6"/>
-      <c r="AH84" s="6"/>
-      <c r="AI84" s="6"/>
-      <c r="AJ84" s="6"/>
-      <c r="AK84" s="6"/>
-      <c r="AL84" s="6"/>
-      <c r="AM84" s="6"/>
-      <c r="AN84" s="9"/>
-      <c r="AO84" s="6"/>
+      <c r="M84" s="5">
+        <v>2798.1999999999998</v>
+      </c>
+      <c r="N84" s="6">
+        <v>29</v>
+      </c>
+      <c r="O84" s="6">
+        <v>22</v>
+      </c>
+      <c r="P84" s="7">
+        <v>4.7910714285714286</v>
+      </c>
+      <c r="Q84" s="8">
+        <v>17.956818181818182</v>
+      </c>
+      <c r="R84" s="8">
+        <v>6.8016649999999998</v>
+      </c>
+      <c r="S84" s="8">
+        <v>7</v>
+      </c>
+      <c r="T84" s="9">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="U84" s="9">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="V84" s="9">
+        <v>0</v>
+      </c>
+      <c r="W84" s="9">
+        <v>0</v>
+      </c>
+      <c r="X84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AB84" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AC84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE84" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL84" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP84" s="4">
         <v>58</v>
       </c>
@@ -16576,7 +16794,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16606,35 +16824,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>2833.5</v>
+      </c>
+      <c r="N102" s="6">
+        <v>28</v>
+      </c>
+      <c r="O102" s="6">
+        <v>16</v>
+      </c>
+      <c r="P102" s="7">
+        <v>11.323455555555554</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>29.908329999999999</v>
+      </c>
+      <c r="R102" s="8">
+        <v>38.731818181818184</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -17023,7 +17299,9 @@
       <c r="N105" s="6">
         <v>13</v>
       </c>
-      <c r="O105" s="6"/>
+      <c r="O105" s="6">
+        <v>6</v>
+      </c>
       <c r="P105" s="7">
         <v>5.8692307692307688</v>
       </c>
@@ -17033,31 +17311,75 @@
       <c r="R105" s="8">
         <v>9.5861166666666673</v>
       </c>
-      <c r="S105" s="8"/>
+      <c r="S105" s="8">
+        <v>6.2999999999999998</v>
+      </c>
       <c r="T105" s="9">
         <v>0</v>
       </c>
-      <c r="U105" s="9"/>
-      <c r="V105" s="9"/>
-      <c r="W105" s="9"/>
-      <c r="X105" s="9"/>
-      <c r="Y105" s="9"/>
-      <c r="Z105" s="9"/>
-      <c r="AA105" s="9"/>
-      <c r="AB105" s="9"/>
-      <c r="AC105" s="9"/>
-      <c r="AD105" s="6"/>
-      <c r="AE105" s="6"/>
-      <c r="AF105" s="6"/>
-      <c r="AG105" s="6"/>
-      <c r="AH105" s="6"/>
-      <c r="AI105" s="6"/>
-      <c r="AJ105" s="6"/>
-      <c r="AK105" s="6"/>
-      <c r="AL105" s="6"/>
-      <c r="AM105" s="6"/>
-      <c r="AN105" s="9"/>
-      <c r="AO105" s="6"/>
+      <c r="U105" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V105" s="9">
+        <v>0</v>
+      </c>
+      <c r="W105" s="9">
+        <v>0</v>
+      </c>
+      <c r="X105" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AC105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE105" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL105" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO105" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP105" s="4">
         <v>58</v>
       </c>
@@ -23895,7 +24217,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -23925,35 +24247,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>1508.8099999999999</v>
+      </c>
+      <c r="N151" s="6">
+        <v>19</v>
+      </c>
+      <c r="O151" s="6">
+        <v>13</v>
+      </c>
+      <c r="P151" s="7">
+        <v>3.2833333333333332</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>13.3141</v>
+      </c>
+      <c r="R151" s="8">
+        <v>3.1097249999999996</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24777,7 +25157,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -24807,35 +25187,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>1083.8499999999999</v>
+      </c>
+      <c r="N157" s="6">
+        <v>15</v>
+      </c>
+      <c r="O157" s="6">
+        <v>11</v>
+      </c>
+      <c r="P157" s="7">
+        <v>5.2855533333333335</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>16.278790909090908</v>
+      </c>
+      <c r="R157" s="8">
+        <v>4.2227272727272727</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -24876,7 +25314,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -24906,35 +25344,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>2400.98</v>
+      </c>
+      <c r="N158" s="6">
+        <v>23</v>
+      </c>
+      <c r="O158" s="6">
+        <v>18</v>
+      </c>
+      <c r="P158" s="7">
+        <v>8.3478260869565215</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>18.74722222222222</v>
+      </c>
+      <c r="R158" s="8">
+        <v>3.5250000000000004</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -25911,7 +26407,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -25941,35 +26437,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>3150.0900000000001</v>
+      </c>
+      <c r="N165" s="6">
+        <v>39</v>
+      </c>
+      <c r="O165" s="6">
+        <v>21</v>
+      </c>
+      <c r="P165" s="7">
+        <v>3.5918794871794875</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>12.161109523809523</v>
+      </c>
+      <c r="R165" s="8">
+        <v>1.1992047619047619</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
@@ -33432,43 +33986,43 @@
         <v>325</v>
       </c>
       <c t="s" r="AC217" s="11">
+        <v>321</v>
+      </c>
+      <c t="s" r="AD217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AD217" s="11">
+      <c t="s" r="AE217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AE217" s="11">
+      <c t="s" r="AF217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AF217" s="11">
+      <c t="s" r="AG217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AG217" s="11">
+      <c t="s" r="AH217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AH217" s="11">
+      <c t="s" r="AI217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AI217" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AJ217" s="11">
+      <c t="s" r="AK217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AK217" s="11">
+      <c t="s" r="AL217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AL217" s="11">
+      <c t="s" r="AM217" s="11">
+        <v>330</v>
+      </c>
+      <c t="s" r="AN217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AM217" s="11">
+      <c t="s" r="AO217" s="11">
         <v>336</v>
-      </c>
-      <c t="s" r="AN217" s="11">
-        <v>337</v>
-      </c>
-      <c t="s" r="AO217" s="11">
-        <v>338</v>
       </c>
       <c r="AP217" s="12"/>
       <c t="s" r="AQ217" s="12">
@@ -33485,10 +34039,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX217" s="11">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c t="s" r="AY217" s="11">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AZ217" s="12"/>
       <c r="BA217" s="12"/>
